--- a/school_enrollment_forms/009_preschool_summer_camp_enrollment_form--school_enrollment_forms.xlsx
+++ b/school_enrollment_forms/009_preschool_summer_camp_enrollment_form--school_enrollment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1010,8 +1010,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'pre-k'}</t>
+          <t>pre-k</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Pre-K'}</t>
+          <t>Pre-K</t>
         </is>
       </c>
     </row>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'kindergarten'}</t>
+          <t>kindergarten</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Kindergarten'}</t>
+          <t>Kindergarten</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'1st_grade'}</t>
+          <t>1st_grade</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': '1st Grade'}</t>
+          <t>1st Grade</t>
         </is>
       </c>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'2nd_grade'}</t>
+          <t>2nd_grade</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': '2nd Grade'}</t>
+          <t>2nd Grade</t>
         </is>
       </c>
     </row>
@@ -1107,12 +1107,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_5,_'label':_'3rd_grade'}</t>
+          <t>3rd_grade</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 5, 'label': '3rd Grade'}</t>
+          <t>3rd Grade</t>
         </is>
       </c>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'card'}</t>
+          <t>card</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Card'}</t>
+          <t>Card</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'transfer'}</t>
+          <t>transfer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Transfer'}</t>
+          <t>Transfer</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'dairy'}</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Dairy'}</t>
+          <t>Dairy</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'gluten'}</t>
+          <t>gluten</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Gluten'}</t>
+          <t>Gluten</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'veggie'}</t>
+          <t>veggie</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Veggie'}</t>
+          <t>Veggie</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_4,_'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 4, 'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'wheel_chair'}</t>
+          <t>wheel_chair</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'Wheel Chair'}</t>
+          <t>Wheel Chair</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'walker'}</t>
+          <t>walker</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'Walker'}</t>
+          <t>Walker</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
